--- a/m1.xlsx
+++ b/m1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3748B2-26AF-4DBD-9176-1920BD8347A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E82AC8-6645-44FC-A551-A7C7DF08235F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1097,8 +1097,12 @@
       <c r="J3" s="12">
         <v>5</v>
       </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="K3" s="12">
+        <v>27</v>
+      </c>
+      <c r="L3" s="12">
+        <v>4</v>
+      </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="6"/>
@@ -1135,8 +1139,12 @@
       <c r="J4" s="12">
         <v>10</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
+      <c r="K4" s="12">
+        <v>34</v>
+      </c>
+      <c r="L4" s="12">
+        <v>8</v>
+      </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="6"/>
@@ -1173,8 +1181,12 @@
       <c r="J5" s="12">
         <v>0</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="12">
+        <v>26</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0</v>
+      </c>
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="6"/>
@@ -1211,8 +1223,12 @@
       <c r="J6" s="12">
         <v>9</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="12">
+        <v>31</v>
+      </c>
+      <c r="L6" s="12">
+        <v>8</v>
+      </c>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="6"/>
@@ -1249,8 +1265,12 @@
       <c r="J7" s="12">
         <v>5</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="K7" s="12">
+        <v>16</v>
+      </c>
+      <c r="L7" s="12">
+        <v>5</v>
+      </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="6"/>
@@ -1287,8 +1307,12 @@
       <c r="J8" s="12">
         <v>6</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="K8" s="12">
+        <v>15</v>
+      </c>
+      <c r="L8" s="12">
+        <v>6</v>
+      </c>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="6"/>
@@ -1325,8 +1349,12 @@
       <c r="J9" s="12">
         <v>7</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="K9" s="12">
+        <v>17</v>
+      </c>
+      <c r="L9" s="12">
+        <v>4</v>
+      </c>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="6"/>
@@ -1363,8 +1391,12 @@
       <c r="J10" s="12">
         <v>10</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+      <c r="K10" s="12">
+        <v>17</v>
+      </c>
+      <c r="L10" s="12">
+        <v>4</v>
+      </c>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="6"/>
@@ -1401,8 +1433,12 @@
       <c r="J11" s="12">
         <v>6</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+      <c r="K11" s="12">
+        <v>15</v>
+      </c>
+      <c r="L11" s="12">
+        <v>6</v>
+      </c>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="6"/>
@@ -1439,8 +1475,12 @@
       <c r="J12" s="12">
         <v>10</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="K12" s="12">
+        <v>34</v>
+      </c>
+      <c r="L12" s="12">
+        <v>8</v>
+      </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="6"/>
@@ -1477,8 +1517,12 @@
       <c r="J13" s="12">
         <v>0</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="K13" s="12">
+        <v>25</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
       <c r="O13" s="6"/>
@@ -1508,8 +1552,12 @@
       <c r="J14" s="12">
         <v>9</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
+      <c r="K14" s="12">
+        <v>15</v>
+      </c>
+      <c r="L14" s="12">
+        <v>6</v>
+      </c>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
       <c r="O14" s="6"/>
@@ -1539,8 +1587,12 @@
       <c r="J15" s="12">
         <v>8</v>
       </c>
-      <c r="K15" s="13"/>
-      <c r="L15" s="12"/>
+      <c r="K15" s="13">
+        <v>29</v>
+      </c>
+      <c r="L15" s="12">
+        <v>6</v>
+      </c>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="P15" s="6"/>
@@ -1569,8 +1621,12 @@
       <c r="J16" s="12">
         <v>0</v>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
+      <c r="K16" s="12">
+        <v>21</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
       <c r="O16" s="6"/>
@@ -1600,8 +1656,12 @@
       <c r="J17" s="12">
         <v>4</v>
       </c>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="K17" s="12">
+        <v>26</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0</v>
+      </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="6"/>
@@ -1638,8 +1698,12 @@
       <c r="J18" s="12">
         <v>10</v>
       </c>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
+      <c r="K18" s="12">
+        <v>36</v>
+      </c>
+      <c r="L18" s="12">
+        <v>8</v>
+      </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
       <c r="O18" s="6"/>
@@ -1676,8 +1740,12 @@
       <c r="J19" s="12">
         <v>9</v>
       </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="K19" s="12">
+        <v>17</v>
+      </c>
+      <c r="L19" s="12">
+        <v>8</v>
+      </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="6"/>
@@ -1714,8 +1782,12 @@
       <c r="J20" s="12">
         <v>6</v>
       </c>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="K20" s="12">
+        <v>31</v>
+      </c>
+      <c r="L20" s="12">
+        <v>7</v>
+      </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="6"/>
@@ -1752,8 +1824,12 @@
       <c r="J21" s="12">
         <v>8</v>
       </c>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="K21" s="12">
+        <v>31</v>
+      </c>
+      <c r="L21" s="12">
+        <v>9</v>
+      </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="6"/>
@@ -1790,8 +1866,12 @@
       <c r="J22" s="12">
         <v>10</v>
       </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="K22" s="12">
+        <v>31</v>
+      </c>
+      <c r="L22" s="12">
+        <v>7</v>
+      </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
       <c r="O22" s="6"/>

--- a/m1.xlsx
+++ b/m1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E82AC8-6645-44FC-A551-A7C7DF08235F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6CCBDD-F93B-4F04-9BE8-033499EA4074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,8 +1087,12 @@
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="E3" s="12">
+        <v>27</v>
+      </c>
+      <c r="F3" s="12">
+        <v>5</v>
+      </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="12">
@@ -1103,8 +1107,12 @@
       <c r="L3" s="12">
         <v>4</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
+      <c r="M3" s="12">
+        <v>32</v>
+      </c>
+      <c r="N3" s="12">
+        <v>8</v>
+      </c>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
@@ -1129,8 +1137,12 @@
       <c r="D4" s="2">
         <v>10</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="E4" s="12">
+        <v>39</v>
+      </c>
+      <c r="F4" s="12">
+        <v>10</v>
+      </c>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12">
@@ -1145,8 +1157,12 @@
       <c r="L4" s="12">
         <v>8</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
+      <c r="M4" s="12">
+        <v>32</v>
+      </c>
+      <c r="N4" s="12">
+        <v>10</v>
+      </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
@@ -1171,8 +1187,12 @@
       <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="E5" s="12">
+        <v>25</v>
+      </c>
+      <c r="F5" s="12">
+        <v>6</v>
+      </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12">
@@ -1187,8 +1207,12 @@
       <c r="L5" s="12">
         <v>0</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
+      <c r="M5" s="12">
+        <v>34</v>
+      </c>
+      <c r="N5" s="12">
+        <v>9</v>
+      </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -1213,8 +1237,12 @@
       <c r="D6" s="2">
         <v>10</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="12">
+        <v>40</v>
+      </c>
+      <c r="F6" s="12">
+        <v>10</v>
+      </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12">
@@ -1229,8 +1257,12 @@
       <c r="L6" s="12">
         <v>8</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
+      <c r="M6" s="12">
+        <v>34</v>
+      </c>
+      <c r="N6" s="12">
+        <v>9</v>
+      </c>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -1255,8 +1287,12 @@
       <c r="D7" s="2">
         <v>0</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="E7" s="12">
+        <v>28</v>
+      </c>
+      <c r="F7" s="12">
+        <v>3</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12">
@@ -1271,8 +1307,12 @@
       <c r="L7" s="12">
         <v>5</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
+      <c r="M7" s="12">
+        <v>30</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0</v>
+      </c>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -1297,8 +1337,12 @@
       <c r="D8" s="2">
         <v>7</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="E8" s="12">
+        <v>28</v>
+      </c>
+      <c r="F8" s="12">
+        <v>7</v>
+      </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12">
@@ -1313,8 +1357,12 @@
       <c r="L8" s="12">
         <v>6</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
+      <c r="M8" s="12">
+        <v>24</v>
+      </c>
+      <c r="N8" s="12">
+        <v>6</v>
+      </c>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
@@ -1339,8 +1387,12 @@
       <c r="D9" s="2">
         <v>7</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="E9" s="12">
+        <v>29</v>
+      </c>
+      <c r="F9" s="12">
+        <v>7</v>
+      </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12">
@@ -1355,8 +1407,12 @@
       <c r="L9" s="12">
         <v>4</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="M9" s="12">
+        <v>33</v>
+      </c>
+      <c r="N9" s="12">
+        <v>10</v>
+      </c>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -1381,8 +1437,12 @@
       <c r="D10" s="2">
         <v>9</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="12">
+        <v>28</v>
+      </c>
+      <c r="F10" s="12">
+        <v>9</v>
+      </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12">
@@ -1397,8 +1457,12 @@
       <c r="L10" s="12">
         <v>4</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
+      <c r="M10" s="12">
+        <v>32</v>
+      </c>
+      <c r="N10" s="12">
+        <v>8</v>
+      </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
@@ -1423,8 +1487,12 @@
       <c r="D11" s="2">
         <v>7</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="12">
+        <v>25</v>
+      </c>
+      <c r="F11" s="12">
+        <v>7</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12">
@@ -1439,8 +1507,12 @@
       <c r="L11" s="12">
         <v>6</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
+      <c r="M11" s="12">
+        <v>33</v>
+      </c>
+      <c r="N11" s="12">
+        <v>7</v>
+      </c>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
@@ -1465,8 +1537,12 @@
       <c r="D12" s="2">
         <v>10</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="12">
+        <v>39</v>
+      </c>
+      <c r="F12" s="12">
+        <v>10</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12">
@@ -1481,8 +1557,12 @@
       <c r="L12" s="12">
         <v>8</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
+      <c r="M12" s="12">
+        <v>39</v>
+      </c>
+      <c r="N12" s="12">
+        <v>10</v>
+      </c>
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1507,8 +1587,12 @@
       <c r="D13" s="2">
         <v>5</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="12">
+        <v>25</v>
+      </c>
+      <c r="F13" s="12">
+        <v>5</v>
+      </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12">
@@ -1523,8 +1607,12 @@
       <c r="L13" s="12">
         <v>0</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
+      <c r="M13" s="12">
+        <v>26</v>
+      </c>
+      <c r="N13" s="12">
+        <v>7</v>
+      </c>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -1542,8 +1630,12 @@
       <c r="D14" s="2">
         <v>9</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="12">
+        <v>27</v>
+      </c>
+      <c r="F14" s="12">
+        <v>9</v>
+      </c>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12">
@@ -1558,8 +1650,12 @@
       <c r="L14" s="12">
         <v>6</v>
       </c>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
+      <c r="M14" s="12">
+        <v>17</v>
+      </c>
+      <c r="N14" s="12">
+        <v>0</v>
+      </c>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -1577,8 +1673,12 @@
       <c r="D15" s="2">
         <v>10</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="12">
+        <v>37</v>
+      </c>
+      <c r="F15" s="12">
+        <v>10</v>
+      </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12">
@@ -1593,8 +1693,12 @@
       <c r="L15" s="12">
         <v>6</v>
       </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
+      <c r="M15" s="12">
+        <v>31</v>
+      </c>
+      <c r="N15" s="12">
+        <v>5</v>
+      </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
     </row>
@@ -1611,8 +1715,12 @@
       <c r="D16" s="2">
         <v>6</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="12">
+        <v>25</v>
+      </c>
+      <c r="F16" s="12">
+        <v>6</v>
+      </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12">
@@ -1627,8 +1735,12 @@
       <c r="L16" s="12">
         <v>0</v>
       </c>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
+      <c r="M16" s="12">
+        <v>33</v>
+      </c>
+      <c r="N16" s="12">
+        <v>0</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1646,8 +1758,12 @@
       <c r="D17" s="2">
         <v>7</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="12">
+        <v>28</v>
+      </c>
+      <c r="F17" s="12">
+        <v>7</v>
+      </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12">
@@ -1662,8 +1778,12 @@
       <c r="L17" s="12">
         <v>0</v>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+      <c r="M17" s="12">
+        <v>28</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1688,8 +1808,12 @@
       <c r="D18" s="2">
         <v>10</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="12">
+        <v>39</v>
+      </c>
+      <c r="F18" s="12">
+        <v>10</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12">
@@ -1704,8 +1828,12 @@
       <c r="L18" s="12">
         <v>8</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="M18" s="12">
+        <v>39</v>
+      </c>
+      <c r="N18" s="12">
+        <v>10</v>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
@@ -1730,8 +1858,12 @@
       <c r="D19" s="2">
         <v>8</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="12">
+        <v>36</v>
+      </c>
+      <c r="F19" s="12">
+        <v>8</v>
+      </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12">
@@ -1746,8 +1878,12 @@
       <c r="L19" s="12">
         <v>8</v>
       </c>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
+      <c r="M19" s="12">
+        <v>30</v>
+      </c>
+      <c r="N19" s="12">
+        <v>8</v>
+      </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -1772,8 +1908,12 @@
       <c r="D20" s="2">
         <v>8</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="12">
+        <v>32</v>
+      </c>
+      <c r="F20" s="12">
+        <v>8</v>
+      </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12">
@@ -1788,8 +1928,12 @@
       <c r="L20" s="12">
         <v>7</v>
       </c>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
+      <c r="M20" s="12">
+        <v>34</v>
+      </c>
+      <c r="N20" s="12">
+        <v>9</v>
+      </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -1814,8 +1958,12 @@
       <c r="D21" s="2">
         <v>8</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="E21" s="12">
+        <v>37</v>
+      </c>
+      <c r="F21" s="12">
+        <v>8</v>
+      </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12">
@@ -1830,8 +1978,12 @@
       <c r="L21" s="12">
         <v>9</v>
       </c>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
+      <c r="M21" s="12">
+        <v>37</v>
+      </c>
+      <c r="N21" s="12">
+        <v>7</v>
+      </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
@@ -1856,8 +2008,12 @@
       <c r="D22" s="2">
         <v>10</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="E22" s="12">
+        <v>39</v>
+      </c>
+      <c r="F22" s="12">
+        <v>10</v>
+      </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12">
@@ -1872,8 +2028,12 @@
       <c r="L22" s="12">
         <v>7</v>
       </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
+      <c r="M22" s="12">
+        <v>34</v>
+      </c>
+      <c r="N22" s="12">
+        <v>10</v>
+      </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>

--- a/m1.xlsx
+++ b/m1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6CCBDD-F93B-4F04-9BE8-033499EA4074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8A6AC1-5029-469C-939D-44B39BACC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,8 +1093,12 @@
       <c r="F3" s="12">
         <v>5</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="G3" s="12">
+        <v>26</v>
+      </c>
+      <c r="H3" s="12">
+        <v>4</v>
+      </c>
       <c r="I3" s="12">
         <v>15</v>
       </c>
@@ -1143,8 +1147,12 @@
       <c r="F4" s="12">
         <v>10</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="G4" s="12">
+        <v>40</v>
+      </c>
+      <c r="H4" s="12">
+        <v>10</v>
+      </c>
       <c r="I4" s="12">
         <v>39</v>
       </c>
@@ -1193,8 +1201,12 @@
       <c r="F5" s="12">
         <v>6</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
+      <c r="G5" s="12">
+        <v>20</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3</v>
+      </c>
       <c r="I5" s="12">
         <v>14</v>
       </c>
@@ -1243,8 +1255,12 @@
       <c r="F6" s="12">
         <v>10</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="G6" s="12">
+        <v>24</v>
+      </c>
+      <c r="H6" s="12">
+        <v>4</v>
+      </c>
       <c r="I6" s="12">
         <v>39</v>
       </c>
@@ -1293,8 +1309,12 @@
       <c r="F7" s="12">
         <v>3</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
+      <c r="G7" s="12">
+        <v>19</v>
+      </c>
+      <c r="H7" s="12">
+        <v>2</v>
+      </c>
       <c r="I7" s="12">
         <v>20</v>
       </c>
@@ -1343,8 +1363,12 @@
       <c r="F8" s="12">
         <v>7</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="G8" s="12">
+        <v>14</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
       <c r="I8" s="12">
         <v>23</v>
       </c>
@@ -1393,8 +1417,12 @@
       <c r="F9" s="12">
         <v>7</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
+      <c r="G9" s="12">
+        <v>22</v>
+      </c>
+      <c r="H9" s="12">
+        <v>3</v>
+      </c>
       <c r="I9" s="12">
         <v>16</v>
       </c>
@@ -1443,8 +1471,12 @@
       <c r="F10" s="12">
         <v>9</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="G10" s="12">
+        <v>26</v>
+      </c>
+      <c r="H10" s="12">
+        <v>6</v>
+      </c>
       <c r="I10" s="12">
         <v>19</v>
       </c>
@@ -1493,8 +1525,12 @@
       <c r="F11" s="12">
         <v>7</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+      <c r="G11" s="12">
+        <v>19</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
       <c r="I11" s="12">
         <v>16</v>
       </c>
@@ -1543,8 +1579,12 @@
       <c r="F12" s="12">
         <v>10</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="G12" s="12">
+        <v>40</v>
+      </c>
+      <c r="H12" s="12">
+        <v>10</v>
+      </c>
       <c r="I12" s="12">
         <v>39</v>
       </c>
@@ -1593,8 +1633,12 @@
       <c r="F13" s="12">
         <v>5</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
+      <c r="G13" s="12">
+        <v>24</v>
+      </c>
+      <c r="H13" s="12">
+        <v>2</v>
+      </c>
       <c r="I13" s="12">
         <v>14</v>
       </c>
@@ -1625,10 +1669,10 @@
         <v>134</v>
       </c>
       <c r="C14" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" s="12">
         <v>27</v>
@@ -1636,13 +1680,17 @@
       <c r="F14" s="12">
         <v>9</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+      <c r="G14" s="12">
+        <v>14</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
       <c r="I14" s="12">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J14" s="12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K14" s="12">
         <v>15</v>
@@ -1679,8 +1727,12 @@
       <c r="F15" s="12">
         <v>10</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
+      <c r="G15" s="12">
+        <v>31</v>
+      </c>
+      <c r="H15" s="12">
+        <v>6</v>
+      </c>
       <c r="I15" s="12">
         <v>33</v>
       </c>
@@ -1721,8 +1773,12 @@
       <c r="F16" s="12">
         <v>6</v>
       </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
+      <c r="G16" s="12">
+        <v>24</v>
+      </c>
+      <c r="H16" s="12">
+        <v>4</v>
+      </c>
       <c r="I16" s="12">
         <v>14</v>
       </c>
@@ -1764,8 +1820,12 @@
       <c r="F17" s="12">
         <v>7</v>
       </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+      <c r="G17" s="12">
+        <v>20</v>
+      </c>
+      <c r="H17" s="12">
+        <v>2</v>
+      </c>
       <c r="I17" s="12">
         <v>20</v>
       </c>
@@ -1814,8 +1874,12 @@
       <c r="F18" s="12">
         <v>10</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+      <c r="G18" s="12">
+        <v>40</v>
+      </c>
+      <c r="H18" s="12">
+        <v>10</v>
+      </c>
       <c r="I18" s="12">
         <v>39</v>
       </c>
@@ -1864,8 +1928,12 @@
       <c r="F19" s="12">
         <v>8</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="G19" s="12">
+        <v>18</v>
+      </c>
+      <c r="H19" s="12">
+        <v>3</v>
+      </c>
       <c r="I19" s="12">
         <v>32</v>
       </c>
@@ -1914,8 +1982,12 @@
       <c r="F20" s="12">
         <v>8</v>
       </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+      <c r="G20" s="12">
+        <v>25</v>
+      </c>
+      <c r="H20" s="12">
+        <v>5</v>
+      </c>
       <c r="I20" s="12">
         <v>24</v>
       </c>
@@ -1964,8 +2036,12 @@
       <c r="F21" s="12">
         <v>8</v>
       </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
+      <c r="G21" s="12">
+        <v>29</v>
+      </c>
+      <c r="H21" s="12">
+        <v>4</v>
+      </c>
       <c r="I21" s="12">
         <v>38</v>
       </c>
@@ -2014,8 +2090,12 @@
       <c r="F22" s="12">
         <v>10</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="G22" s="12">
+        <v>40</v>
+      </c>
+      <c r="H22" s="12">
+        <v>10</v>
+      </c>
       <c r="I22" s="12">
         <v>39</v>
       </c>

--- a/m1.xlsx
+++ b/m1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8A6AC1-5029-469C-939D-44B39BACC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2131D91A-45B7-44BF-A99F-A7969549EBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -544,7 +544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,6 +554,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,6 +679,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1668,23 +1679,23 @@
       <c r="B14" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="24">
         <v>14</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="24">
         <v>7</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="23">
         <v>27</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="23">
         <v>9</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="23">
         <v>14</v>
       </c>
-      <c r="H14" s="12">
-        <v>0</v>
+      <c r="H14" s="23">
+        <v>3</v>
       </c>
       <c r="I14" s="12">
         <v>14</v>
@@ -1692,19 +1703,19 @@
       <c r="J14" s="12">
         <v>7</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="23">
         <v>15</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="23">
         <v>6</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="23">
         <v>17</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="23">
         <v>0</v>
       </c>
-      <c r="O14" s="6"/>
+      <c r="O14" s="25"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
